--- a/Result/profitability/2421.xlsx
+++ b/Result/profitability/2421.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.14</v>
       </c>
       <c r="M2" t="n">
-        <v>1.63</v>
+        <v>1.77125</v>
       </c>
       <c r="N2" t="n">
-        <v>29.5375</v>
+        <v>29.8825</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.28</v>
       </c>
       <c r="M3" t="n">
-        <v>1.505</v>
+        <v>1.60625</v>
       </c>
       <c r="N3" t="n">
-        <v>28.45</v>
+        <v>28.56375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.47</v>
       </c>
       <c r="M4" t="n">
-        <v>1.36375</v>
+        <v>1.44875</v>
       </c>
       <c r="N4" t="n">
-        <v>27.91125</v>
+        <v>28.16</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.04</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1525</v>
+        <v>1.2825</v>
       </c>
       <c r="N5" t="n">
-        <v>26.56</v>
+        <v>26.65</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.39</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9325</v>
+        <v>0.915</v>
       </c>
       <c r="N6" t="n">
-        <v>24.09875</v>
+        <v>24.08875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.13</v>
       </c>
       <c r="M7" t="n">
-        <v>0.63</v>
+        <v>0.645</v>
       </c>
       <c r="N7" t="n">
-        <v>23.45125</v>
+        <v>23.255</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.66</v>
       </c>
       <c r="M8" t="n">
-        <v>0.42625</v>
+        <v>0.4325</v>
       </c>
       <c r="N8" t="n">
-        <v>22.99625</v>
+        <v>22.945</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>5419</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3725</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1693</v>
+      </c>
+      <c r="F75" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="G75" t="n">
+        <v>836</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>15.43%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>76</v>
+      </c>
+      <c r="J75" t="n">
+        <v>912</v>
+      </c>
+      <c r="K75" t="n">
+        <v>690</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.94875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>30.71</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.05000000000000027</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.02118644067796627</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.4100000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.01295009475679088</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.7591240875912408</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.7199999999999989</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.02358336062888955</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
